--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.14890930562984</v>
+        <v>4.411697762164849</v>
       </c>
       <c r="D2" t="n">
-        <v>26.47209472592387</v>
+        <v>4.301715392962628</v>
       </c>
       <c r="E2" t="n">
-        <v>8.920319014167159</v>
+        <v>1.449551839802163</v>
       </c>
       <c r="F2" t="n">
-        <v>8.516810328125834</v>
+        <v>1.383981678320448</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.78967085423683</v>
+        <v>4.515821513813485</v>
       </c>
       <c r="D3" t="n">
-        <v>27.13919870130842</v>
+        <v>4.410119788962618</v>
       </c>
       <c r="E3" t="n">
-        <v>8.920319014167159</v>
+        <v>1.449551839802163</v>
       </c>
       <c r="F3" t="n">
-        <v>8.516810328125834</v>
+        <v>1.383981678320448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.70409414331078</v>
+        <v>5.476915298288002</v>
       </c>
       <c r="D4" t="n">
-        <v>33.60987011906924</v>
+        <v>5.461603894348752</v>
       </c>
       <c r="E4" t="n">
-        <v>8.920319014167159</v>
+        <v>1.449551839802163</v>
       </c>
       <c r="F4" t="n">
-        <v>8.516810328125834</v>
+        <v>1.383981678320448</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.681579044838728</v>
+        <v>1.248256594786293</v>
       </c>
       <c r="D5" t="n">
-        <v>8.416438930205233</v>
+        <v>1.36767132615835</v>
       </c>
       <c r="E5" t="n">
-        <v>8.920319014167159</v>
+        <v>1.449551839802163</v>
       </c>
       <c r="F5" t="n">
-        <v>8.516810328125834</v>
+        <v>1.383981678320448</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.47869321035568</v>
+        <v>5.602787646682798</v>
       </c>
       <c r="D6" t="n">
-        <v>33.60987014354674</v>
+        <v>5.461603898326346</v>
       </c>
       <c r="E6" t="n">
-        <v>8.920319014167159</v>
+        <v>1.449551839802163</v>
       </c>
       <c r="F6" t="n">
-        <v>8.516810328125834</v>
+        <v>1.383981678320448</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.42576352234731</v>
+        <v>3.806686572381439</v>
       </c>
       <c r="D7" t="n">
-        <v>22.59856949026133</v>
+        <v>3.672267542167466</v>
       </c>
       <c r="E7" t="n">
-        <v>8.920319014167159</v>
+        <v>1.449551839802163</v>
       </c>
       <c r="F7" t="n">
-        <v>8.516810328125834</v>
+        <v>1.383981678320448</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
